--- a/out/MLP-Mamba1_metrics.xlsx
+++ b/out/MLP-Mamba1_metrics.xlsx
@@ -472,7 +472,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.548771721124649</v>
+        <v>0.5487717092037201</v>
       </c>
       <c r="B2" t="n">
         <v>0.4273222088813782</v>
